--- a/Versão5/ABNT/Ontologia_15965_3E.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3E.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3C914D-9CC6-44C4-A43F-CA31E2229818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -6418,63 +6418,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7762E94B-0EF8-4169-A51C-F9B49B760C57}"/>
   </cellStyles>
-  <dxfs count="75">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="69">
     <dxf>
       <font>
         <b val="0"/>
@@ -8189,33 +8133,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71" totalsRowBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8740,7 +8684,7 @@
       </c>
       <c r="B18" s="19">
         <f ca="1">NOW()</f>
-        <v>46167.413725115737</v>
+        <v>46214.346858101853</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>1529</v>
@@ -9442,7 +9386,7 @@
         <v>745</v>
       </c>
       <c r="L7" s="56" t="str">
-        <f t="shared" ref="L2:N17" si="4">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="56" t="str">
@@ -14868,29 +14812,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A66">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA19">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:A66">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15042,7 +14976,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15087,7 +15021,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70720,26 +70654,26 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q4">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:S4">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U4">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:Y4 X5:Y722 V723:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_3E.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3E.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487C74CC-96B8-4029-88BA-16526030472C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABC6C3E-B38C-4511-9169-B74264AD57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18639" uniqueCount="1924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18639" uniqueCount="1923">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5847,9 +5847,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -6382,63 +6379,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7762E94B-0EF8-4169-A51C-F9B49B760C57}"/>
   </cellStyles>
-  <dxfs count="75">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="69">
     <dxf>
       <font>
         <b val="0"/>
@@ -8153,33 +8094,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="74" dataDxfId="72" headerRowBorderDxfId="73" tableBorderDxfId="71" totalsRowBorderDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="68" dataDxfId="66" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="69" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="67" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="65" dataDxfId="64"/>
-    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="63" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="61" dataDxfId="60"/>
-    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="59" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="57" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="55" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="53" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="51" dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="49" dataDxfId="48"/>
-    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="47" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="45" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="43" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="41" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="39" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="37" dataDxfId="36"/>
-    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="35" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="33" dataDxfId="32"/>
-    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="31" dataDxfId="30"/>
-    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="29" dataDxfId="28"/>
-    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="27" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="25" dataDxfId="24"/>
-    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="23" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="63" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="61" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="59" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="57" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="55" dataDxfId="54"/>
+    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="53" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="51" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="49" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="47" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="45" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="43" dataDxfId="42"/>
+    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="41" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="39" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="37" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="35" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="33" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="31" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="29" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="27" dataDxfId="26"/>
+    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="25" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="23" dataDxfId="22"/>
+    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="21" dataDxfId="20"/>
+    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="19" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="17" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="15" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8704,7 +8645,7 @@
       </c>
       <c r="B18" s="19">
         <f ca="1">NOW()</f>
-        <v>46216.266569907406</v>
+        <v>46219.571842824073</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>1528</v>
@@ -8809,7 +8750,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67B40A7-0299-43C5-B399-F7F9056DD3F6}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA66"/>
-  <sheetFormatPr defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.83203125" style="33" customWidth="1"/>
@@ -8833,7 +8774,7 @@
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>1471</v>
       </c>
@@ -8916,7 +8857,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -8988,7 +8929,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>1918</v>
+        <v>1551</v>
       </c>
       <c r="W2" s="60" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -9001,14 +8942,14 @@
         <v>745</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="AA2" s="37" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -9059,7 +9000,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="Q3" s="37" t="s">
         <v>1917</v>
@@ -9080,7 +9021,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>1918</v>
+        <v>1551</v>
       </c>
       <c r="W3" s="60" t="str">
         <f t="shared" ref="W3:W66" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -9100,7 +9041,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -9151,7 +9092,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="Q4" s="37" t="s">
         <v>1917</v>
@@ -9172,7 +9113,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>1918</v>
+        <v>1551</v>
       </c>
       <c r="W4" s="60" t="str">
         <f t="shared" si="4"/>
@@ -9192,7 +9133,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -9243,7 +9184,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="Q5" s="37" t="s">
         <v>1917</v>
@@ -9264,7 +9205,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>1918</v>
+        <v>1551</v>
       </c>
       <c r="W5" s="60" t="str">
         <f t="shared" si="4"/>
@@ -9284,7 +9225,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -9335,7 +9276,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="Q6" s="37" t="s">
         <v>1917</v>
@@ -9356,7 +9297,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>1918</v>
+        <v>1551</v>
       </c>
       <c r="W6" s="60" t="str">
         <f t="shared" si="4"/>
@@ -9376,7 +9317,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -9467,7 +9408,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -9558,7 +9499,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -9649,7 +9590,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -9740,7 +9681,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -9831,7 +9772,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -9922,7 +9863,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -10013,7 +9954,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -10104,7 +10045,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -10195,7 +10136,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -10286,7 +10227,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -10377,7 +10318,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -10468,7 +10409,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -10559,7 +10500,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -10650,7 +10591,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -10741,7 +10682,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -10832,7 +10773,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -10923,7 +10864,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -11014,7 +10955,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -11105,7 +11046,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -11196,7 +11137,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -11287,7 +11228,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -11378,7 +11319,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -11469,7 +11410,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -11560,7 +11501,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -11651,7 +11592,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -11742,7 +11683,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50">
         <v>33</v>
       </c>
@@ -11833,7 +11774,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50">
         <v>34</v>
       </c>
@@ -11924,7 +11865,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50">
         <v>35</v>
       </c>
@@ -12015,7 +11956,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50">
         <v>36</v>
       </c>
@@ -12106,7 +12047,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="50">
         <v>37</v>
       </c>
@@ -12197,7 +12138,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="50">
         <v>38</v>
       </c>
@@ -12288,7 +12229,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="50">
         <v>39</v>
       </c>
@@ -12379,7 +12320,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="50">
         <v>40</v>
       </c>
@@ -12470,7 +12411,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="50">
         <v>41</v>
       </c>
@@ -12561,7 +12502,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="50">
         <v>42</v>
       </c>
@@ -12652,7 +12593,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50">
         <v>43</v>
       </c>
@@ -12743,7 +12684,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="50">
         <v>44</v>
       </c>
@@ -12834,7 +12775,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="50">
         <v>45</v>
       </c>
@@ -12925,7 +12866,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="50">
         <v>46</v>
       </c>
@@ -13016,7 +12957,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="50">
         <v>47</v>
       </c>
@@ -13107,7 +13048,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="50">
         <v>48</v>
       </c>
@@ -13198,7 +13139,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="50">
         <v>49</v>
       </c>
@@ -13289,7 +13230,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="50">
         <v>50</v>
       </c>
@@ -13380,7 +13321,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="50">
         <v>51</v>
       </c>
@@ -13471,7 +13412,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="50">
         <v>52</v>
       </c>
@@ -13562,7 +13503,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="50">
         <v>53</v>
       </c>
@@ -13653,7 +13594,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="50">
         <v>54</v>
       </c>
@@ -13744,7 +13685,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="50">
         <v>55</v>
       </c>
@@ -13835,7 +13776,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="50">
         <v>56</v>
       </c>
@@ -13926,7 +13867,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50">
         <v>57</v>
       </c>
@@ -14017,7 +13958,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="50">
         <v>58</v>
       </c>
@@ -14108,7 +14049,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="50">
         <v>59</v>
       </c>
@@ -14199,7 +14140,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="50">
         <v>60</v>
       </c>
@@ -14290,7 +14231,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="50">
         <v>61</v>
       </c>
@@ -14381,7 +14322,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="50">
         <v>62</v>
       </c>
@@ -14472,7 +14413,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="50">
         <v>63</v>
       </c>
@@ -14563,7 +14504,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="50">
         <v>64</v>
       </c>
@@ -14654,7 +14595,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="50">
         <v>65</v>
       </c>
@@ -14745,7 +14686,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="50">
         <v>66</v>
       </c>
@@ -14837,29 +14778,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A66">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA19">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B66">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B66">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15011,7 +14942,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15056,7 +14987,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70689,26 +70620,26 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q4">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:S4">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U4">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:Y4 X5:Y722 V723:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_3E.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3E.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86688724-6E09-4188-B5B9-4B92053F8C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02BB3C0-20A3-45E0-8541-C4D6A3F353C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18639" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18678" uniqueCount="1955">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -5880,13 +5880,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -5974,8 +6052,34 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6132,6 +6236,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -6207,11 +6317,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6392,38 +6503,31 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7762E94B-0EF8-4169-A51C-F9B49B760C57}"/>
   </cellStyles>
-  <dxfs count="72">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <font>
         <b val="0"/>
@@ -6499,6 +6603,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -8138,33 +8252,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68" totalsRowBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A07C259E-03F8-41A3-821C-289758C0BF1B}" name="Tabla2" displayName="Tabla2" ref="A2:Y722" headerRowCount="0" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="66" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="64" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="62" dataDxfId="61"/>
-    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="60" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="58" dataDxfId="57"/>
-    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="56" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="54" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="52" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="50" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="48" dataDxfId="47"/>
-    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="46" dataDxfId="45"/>
-    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="44" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="42" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="40" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="38" dataDxfId="37"/>
-    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="36" dataDxfId="35"/>
-    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="34" dataDxfId="33"/>
-    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="32" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="30" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="28" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="26" dataDxfId="25"/>
-    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="24" dataDxfId="23"/>
-    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="22" dataDxfId="21"/>
-    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="20" dataDxfId="19"/>
-    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{D841A366-4823-4EF9-B009-219AA94AF50A}" name="1" headerRowDxfId="64" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{41E717E1-E3DE-44C1-91C4-719DAB59A464}" name="Indivíduo" headerRowDxfId="62" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{38346B1D-47C6-4B44-A19C-766D16435669}" name="Classe" headerRowDxfId="60" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{7E912914-9569-4822-984C-7A1AF4C10EAE}" name="Coluna8" headerRowDxfId="58" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{CDA30AA3-6CC0-4D6B-AA3D-8201E7A1023C}" name="Coluna7" headerRowDxfId="56" dataDxfId="55"/>
+    <tableColumn id="26" xr3:uid="{14DEC38B-5BC0-4C90-8E5C-1E35ACBA832D}" name="Coluna19" headerRowDxfId="54" dataDxfId="53"/>
+    <tableColumn id="13" xr3:uid="{40ED8FBD-39D6-4C0F-867B-9AA8C9C09316}" name="Valor8" headerRowDxfId="52" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{CA2BF8F3-B237-40DC-9F32-AE22CDD6890C}" name="Coluna1" headerRowDxfId="50" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{36C796DC-6C7E-4B41-87B9-9FCF9B82EE70}" name="Coluna2" headerRowDxfId="48" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{56BA1A67-ABAC-4289-86BE-471F0E0A5E64}" name="Coluna3" headerRowDxfId="46" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{359EFFF9-0CB6-41EE-8805-290113822D31}" name="Coluna4" headerRowDxfId="44" dataDxfId="43"/>
+    <tableColumn id="24" xr3:uid="{4E625920-945F-4868-96CA-1E9865A82F1B}" name="Coluna21" headerRowDxfId="42" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{A045FBDA-3EB3-48DF-8B48-041D1CD62621}" name="Coluna20" headerRowDxfId="40" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{482EF924-06FF-4A9E-8F53-CA8519E91C6A}" name="Coluna5" headerRowDxfId="38" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{B772DC13-CA24-463F-93C9-F7821EBCC314}" name="Coluna6" headerRowDxfId="36" dataDxfId="35"/>
+    <tableColumn id="14" xr3:uid="{7C5E1ACB-9144-4A9B-BE11-C1C1B7337842}" name="Coluna9" headerRowDxfId="34" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{D82361B2-6609-4711-ABE0-509E1D365618}" name="Coluna10" headerRowDxfId="32" dataDxfId="31"/>
+    <tableColumn id="16" xr3:uid="{FA89BFC3-A470-4C5B-8EDE-3888662AD6DF}" name="Coluna11" headerRowDxfId="30" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{7461A7D5-3F34-4122-877D-BA99287C1DDC}" name="Coluna12" headerRowDxfId="28" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{90564319-2742-4584-A135-64808AD65253}" name="Coluna13" headerRowDxfId="26" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{5AD80C80-D087-4B6C-8A72-CF0A5AA8E9C5}" name="Coluna14" headerRowDxfId="24" dataDxfId="23"/>
+    <tableColumn id="20" xr3:uid="{ADCE9408-1D25-4A86-896A-DC3040DCC77A}" name="Coluna15" headerRowDxfId="22" dataDxfId="21"/>
+    <tableColumn id="21" xr3:uid="{E9E06793-AB89-4B33-B62D-508D99B8AE8B}" name="Coluna16" headerRowDxfId="20" dataDxfId="19"/>
+    <tableColumn id="22" xr3:uid="{E1409F83-40B1-4B25-89A1-45CE84A94FDA}" name="Coluna17" headerRowDxfId="18" dataDxfId="17"/>
+    <tableColumn id="23" xr3:uid="{FFF4EFB8-C5DF-42B3-8EE2-618A27B1C442}" name="Coluna18" headerRowDxfId="16" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -8488,7 +8602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6150FAF1-0727-432D-9C9B-B6DB6881C7C4}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
@@ -8689,7 +8803,7 @@
       </c>
       <c r="B18" s="19">
         <f ca="1">NOW()</f>
-        <v>46232.783922106479</v>
+        <v>46233.479511805555</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>1527</v>
@@ -8785,7 +8899,157 @@
         <v>1529</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B27" s="62" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B32" s="64" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="16" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B33" s="66" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B34" s="66" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B35" s="64" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="16" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B36" s="66" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="16" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B37" s="64" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="18" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B38" s="67" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="69" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="16" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B39" s="68" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>1527</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{CC439A2C-1A65-4B54-AD0E-B0E341AF2C17}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{C6DB31A9-6939-4B27-8B16-BB660AC209DD}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{453F3C9E-8DD0-4144-8578-62C9184A6C42}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{AE89E085-92B6-435C-AABC-9D3D6DD49EE4}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{CC90B129-6E4B-4485-8703-04E4E70A2B25}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -14822,32 +15086,22 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B66">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B66">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14999,7 +15253,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15044,7 +15298,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -70677,26 +70931,26 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q4">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:S4">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U4">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:Y4 X5:Y722 V723:Y1048576">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_3E.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3E.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02BB3C0-20A3-45E0-8541-C4D6A3F353C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -8603,14 +8603,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6150FAF1-0727-432D-9C9B-B6DB6881C7C4}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="20.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>3</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>728</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>729</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>4</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>5</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>6</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>7</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>8</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>732</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>734</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
         <v>735</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>9</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>736</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>737</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>738</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>739</v>
       </c>
@@ -8786,7 +8786,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
         <v>11</v>
       </c>
@@ -8797,19 +8797,19 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>740</v>
       </c>
       <c r="B18" s="19">
         <f ca="1">NOW()</f>
-        <v>46233.479511805555</v>
+        <v>46237.685275462965</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>1527</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
         <v>1537</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
         <v>1531</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
         <v>1538</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>727</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>741</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
         <v>1465</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
         <v>1467</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>1523</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>1929</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>1931</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>1933</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="16" t="s">
         <v>1935</v>
       </c>
@@ -8943,7 +8943,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="16" t="s">
         <v>1937</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="16" t="s">
         <v>1939</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="16" t="s">
         <v>1941</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="16" t="s">
         <v>1943</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="16" t="s">
         <v>1945</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="16" t="s">
         <v>1947</v>
       </c>
@@ -9009,7 +9009,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="65" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="16" t="s">
         <v>1949</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="18" t="s">
         <v>1951</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="69" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="69" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="16" t="s">
         <v>1953</v>
       </c>
@@ -9058,31 +9058,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67B40A7-0299-43C5-B399-F7F9056DD3F6}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA66"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.796875" style="33" customWidth="1"/>
-    <col min="4" max="4" width="8.296875" style="33" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="33" customWidth="1"/>
-    <col min="6" max="6" width="16.296875" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.69921875" style="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.83203125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="33" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.6640625" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="9.296875" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="62" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="70" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.796875" style="33" customWidth="1"/>
-    <col min="19" max="19" width="8.296875" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" style="33" customWidth="1"/>
+    <col min="19" max="19" width="8.33203125" customWidth="1"/>
     <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="10.19921875" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" customWidth="1"/>
-    <col min="23" max="23" width="8.69921875" style="33" customWidth="1"/>
-    <col min="26" max="26" width="11.19921875" customWidth="1"/>
+    <col min="21" max="21" width="10.1640625" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" style="33" customWidth="1"/>
+    <col min="26" max="26" width="11.1640625" customWidth="1"/>
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
         <v>1471</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="50">
         <v>2</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="50">
         <v>3</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="50">
         <v>4</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="50">
         <v>5</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="50">
         <v>6</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="50">
         <v>7</v>
       </c>
@@ -9716,7 +9716,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="50">
         <v>8</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="50">
         <v>11</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="50">
         <v>12</v>
       </c>
@@ -10171,7 +10171,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="50">
         <v>13</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="50">
         <v>14</v>
       </c>
@@ -10353,7 +10353,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="50">
         <v>15</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="50">
         <v>16</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="50">
         <v>17</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="50">
         <v>18</v>
       </c>
@@ -10717,7 +10717,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="50">
         <v>19</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50">
         <v>20</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="50">
         <v>21</v>
       </c>
@@ -10990,7 +10990,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="50">
         <v>22</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="50">
         <v>23</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="50">
         <v>24</v>
       </c>
@@ -11263,7 +11263,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="50">
         <v>25</v>
       </c>
@@ -11354,7 +11354,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="50">
         <v>26</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="50">
         <v>27</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="50">
         <v>28</v>
       </c>
@@ -11627,7 +11627,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="50">
         <v>29</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="50">
         <v>30</v>
       </c>
@@ -11809,7 +11809,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="50">
         <v>31</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="50">
         <v>32</v>
       </c>
@@ -11991,7 +11991,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50">
         <v>33</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="50">
         <v>34</v>
       </c>
@@ -12173,7 +12173,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="50">
         <v>35</v>
       </c>
@@ -12264,7 +12264,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="50">
         <v>36</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="50">
         <v>37</v>
       </c>
@@ -12446,7 +12446,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="50">
         <v>38</v>
       </c>
@@ -12537,7 +12537,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="50">
         <v>39</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="50">
         <v>40</v>
       </c>
@@ -12719,7 +12719,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="50">
         <v>41</v>
       </c>
@@ -12810,7 +12810,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="50">
         <v>42</v>
       </c>
@@ -12901,7 +12901,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50">
         <v>43</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="50">
         <v>44</v>
       </c>
@@ -13083,7 +13083,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="50">
         <v>45</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="50">
         <v>46</v>
       </c>
@@ -13265,7 +13265,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="50">
         <v>47</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="50">
         <v>48</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="50">
         <v>49</v>
       </c>
@@ -13538,7 +13538,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="50">
         <v>50</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="50">
         <v>51</v>
       </c>
@@ -13720,7 +13720,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="50">
         <v>52</v>
       </c>
@@ -13811,7 +13811,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="50">
         <v>53</v>
       </c>
@@ -13902,7 +13902,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="50">
         <v>54</v>
       </c>
@@ -13993,7 +13993,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="50">
         <v>55</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="50">
         <v>56</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50">
         <v>57</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="50">
         <v>58</v>
       </c>
@@ -14357,7 +14357,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="50">
         <v>59</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="50">
         <v>60</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="50">
         <v>61</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="50">
         <v>62</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="50">
         <v>63</v>
       </c>
@@ -14812,7 +14812,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="50">
         <v>64</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="50">
         <v>65</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="50">
         <v>66</v>
       </c>
@@ -15116,12 +15116,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DB9369-35E2-4B4D-AD06-DBCD66EE066B}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
         <v>1472</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="26">
         <v>2</v>
       </c>
@@ -15268,13 +15268,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5205260-7147-44D2-9997-02AF0D1204E5}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.296875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="29">
         <v>1</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -15310,35 +15310,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y722"/>
-  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.69921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.296875" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="5" customWidth="1"/>
     <col min="6" max="6" width="5" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.69921875" style="44" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="44" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" style="44" customWidth="1"/>
-    <col min="9" max="9" width="5.69921875" style="44" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" style="44" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="44" customWidth="1"/>
-    <col min="11" max="11" width="16.69921875" style="44" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="44" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" style="5" customWidth="1"/>
-    <col min="13" max="13" width="21.19921875" style="5" customWidth="1"/>
+    <col min="13" max="13" width="21.1640625" style="5" customWidth="1"/>
     <col min="14" max="14" width="7" style="44" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="52.19921875" style="44" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.296875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="5.69921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="52.1640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="5" customWidth="1"/>
-    <col min="19" max="19" width="6.69921875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" style="5" customWidth="1"/>
     <col min="20" max="20" width="6" style="5" customWidth="1"/>
-    <col min="21" max="21" width="6.69921875" style="5" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" style="5" customWidth="1"/>
     <col min="22" max="22" width="5" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="3.796875" style="5" customWidth="1"/>
-    <col min="26" max="16384" width="11.296875" style="5"/>
+    <col min="23" max="25" width="3.83203125" style="5" customWidth="1"/>
+    <col min="26" max="16384" width="11.33203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>742</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -15719,7 +15719,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -16335,7 +16335,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -16412,7 +16412,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -16720,7 +16720,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -16797,7 +16797,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -16874,7 +16874,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -17028,7 +17028,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -17105,7 +17105,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -17336,7 +17336,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -17413,7 +17413,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -17490,7 +17490,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -17644,7 +17644,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -17798,7 +17798,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -18029,7 +18029,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -18106,7 +18106,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -18183,7 +18183,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -18260,7 +18260,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -18337,7 +18337,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -18414,7 +18414,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -18568,7 +18568,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -18645,7 +18645,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -18722,7 +18722,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -18799,7 +18799,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -18953,7 +18953,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -19030,7 +19030,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -19184,7 +19184,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -19261,7 +19261,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -19415,7 +19415,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -19492,7 +19492,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -19646,7 +19646,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -19723,7 +19723,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -19800,7 +19800,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -19877,7 +19877,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -19954,7 +19954,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -20108,7 +20108,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -20185,7 +20185,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -20339,7 +20339,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -20416,7 +20416,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -20493,7 +20493,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -20570,7 +20570,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -20647,7 +20647,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -20724,7 +20724,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -20801,7 +20801,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -20955,7 +20955,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -21032,7 +21032,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -21109,7 +21109,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -21186,7 +21186,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -21263,7 +21263,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -21340,7 +21340,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -21417,7 +21417,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -21494,7 +21494,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -21571,7 +21571,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -21725,7 +21725,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -21802,7 +21802,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -21879,7 +21879,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -21956,7 +21956,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -22033,7 +22033,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -22110,7 +22110,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -22187,7 +22187,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -22264,7 +22264,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -22341,7 +22341,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -22495,7 +22495,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -22572,7 +22572,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -22649,7 +22649,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -22726,7 +22726,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -22803,7 +22803,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -22880,7 +22880,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -22957,7 +22957,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -23034,7 +23034,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -23111,7 +23111,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -23265,7 +23265,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -23419,7 +23419,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -23496,7 +23496,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -23573,7 +23573,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -23650,7 +23650,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -23727,7 +23727,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -23804,7 +23804,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -23881,7 +23881,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -23958,7 +23958,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -24035,7 +24035,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -24112,7 +24112,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -24189,7 +24189,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -24266,7 +24266,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -24343,7 +24343,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -24420,7 +24420,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -24497,7 +24497,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -24574,7 +24574,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -24651,7 +24651,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -24728,7 +24728,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -24805,7 +24805,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -24882,7 +24882,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -24959,7 +24959,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -25036,7 +25036,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -25113,7 +25113,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -25190,7 +25190,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -25267,7 +25267,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -25344,7 +25344,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -25421,7 +25421,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -25498,7 +25498,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -25575,7 +25575,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -25652,7 +25652,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -25729,7 +25729,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -25806,7 +25806,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -25883,7 +25883,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -25960,7 +25960,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -26037,7 +26037,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -26114,7 +26114,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -26191,7 +26191,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -26268,7 +26268,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -26345,7 +26345,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -26422,7 +26422,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -26499,7 +26499,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -26576,7 +26576,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -26653,7 +26653,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -26730,7 +26730,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -26807,7 +26807,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -26884,7 +26884,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -26961,7 +26961,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -27038,7 +27038,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -27115,7 +27115,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -27192,7 +27192,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -27269,7 +27269,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -27346,7 +27346,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -27500,7 +27500,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -27577,7 +27577,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -27654,7 +27654,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -27731,7 +27731,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -27808,7 +27808,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -27885,7 +27885,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -27962,7 +27962,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -28039,7 +28039,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -28116,7 +28116,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -28193,7 +28193,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -28270,7 +28270,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -28347,7 +28347,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -28424,7 +28424,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -28501,7 +28501,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -28578,7 +28578,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -28655,7 +28655,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -28732,7 +28732,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -28809,7 +28809,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -28886,7 +28886,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -28963,7 +28963,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -29040,7 +29040,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -29117,7 +29117,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -29194,7 +29194,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -29271,7 +29271,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -29348,7 +29348,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -29425,7 +29425,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -29502,7 +29502,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -29579,7 +29579,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -29656,7 +29656,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -29733,7 +29733,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -29810,7 +29810,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -29887,7 +29887,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -29964,7 +29964,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -30041,7 +30041,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -30118,7 +30118,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -30195,7 +30195,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -30272,7 +30272,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -30349,7 +30349,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -30426,7 +30426,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -30503,7 +30503,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -30580,7 +30580,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -30657,7 +30657,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -30734,7 +30734,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -30811,7 +30811,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -30888,7 +30888,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -30965,7 +30965,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -31042,7 +31042,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -31119,7 +31119,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -31196,7 +31196,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -31273,7 +31273,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -31350,7 +31350,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -31427,7 +31427,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -31504,7 +31504,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -31581,7 +31581,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -31658,7 +31658,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -31735,7 +31735,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -31812,7 +31812,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -31889,7 +31889,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -31966,7 +31966,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -32043,7 +32043,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -32120,7 +32120,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -32197,7 +32197,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -32274,7 +32274,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -32351,7 +32351,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -32428,7 +32428,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -32505,7 +32505,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -32582,7 +32582,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -32659,7 +32659,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -32736,7 +32736,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -32813,7 +32813,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -32890,7 +32890,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -32967,7 +32967,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -33044,7 +33044,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -33121,7 +33121,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -33198,7 +33198,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -33275,7 +33275,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -33352,7 +33352,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -33429,7 +33429,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -33506,7 +33506,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -33583,7 +33583,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -33660,7 +33660,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -33737,7 +33737,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -33814,7 +33814,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -33891,7 +33891,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -33968,7 +33968,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -34045,7 +34045,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -34122,7 +34122,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -34199,7 +34199,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -34276,7 +34276,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -34353,7 +34353,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -34430,7 +34430,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -34507,7 +34507,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -34584,7 +34584,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -34661,7 +34661,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -34738,7 +34738,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -34815,7 +34815,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -34892,7 +34892,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -34969,7 +34969,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -35046,7 +35046,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -35123,7 +35123,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -35200,7 +35200,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -35277,7 +35277,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -35354,7 +35354,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -35431,7 +35431,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -35508,7 +35508,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -35585,7 +35585,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -35662,7 +35662,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -35739,7 +35739,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -35816,7 +35816,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -35893,7 +35893,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -35970,7 +35970,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -36047,7 +36047,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -36124,7 +36124,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -36201,7 +36201,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -36278,7 +36278,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -36355,7 +36355,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -36432,7 +36432,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -36509,7 +36509,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -36586,7 +36586,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -36663,7 +36663,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -36740,7 +36740,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -36817,7 +36817,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -36894,7 +36894,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -36971,7 +36971,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -37048,7 +37048,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -37125,7 +37125,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -37202,7 +37202,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -37279,7 +37279,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -37356,7 +37356,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -37433,7 +37433,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -37510,7 +37510,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -37587,7 +37587,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -37664,7 +37664,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -37741,7 +37741,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -37818,7 +37818,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -37895,7 +37895,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -37972,7 +37972,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -38049,7 +38049,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -38126,7 +38126,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -38203,7 +38203,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -38280,7 +38280,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -38357,7 +38357,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -38434,7 +38434,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -38511,7 +38511,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -38588,7 +38588,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>303</v>
       </c>
@@ -38665,7 +38665,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="6">
         <v>304</v>
       </c>
@@ -38742,7 +38742,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="6">
         <v>305</v>
       </c>
@@ -38819,7 +38819,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="6">
         <v>306</v>
       </c>
@@ -38896,7 +38896,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="6">
         <v>307</v>
       </c>
@@ -38973,7 +38973,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="6">
         <v>308</v>
       </c>
@@ -39050,7 +39050,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="6">
         <v>309</v>
       </c>
@@ -39127,7 +39127,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="6">
         <v>310</v>
       </c>
@@ -39204,7 +39204,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="6">
         <v>311</v>
       </c>
@@ -39281,7 +39281,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="6">
         <v>312</v>
       </c>
@@ -39358,7 +39358,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="6">
         <v>313</v>
       </c>
@@ -39435,7 +39435,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="6">
         <v>314</v>
       </c>
@@ -39512,7 +39512,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="6">
         <v>315</v>
       </c>
@@ -39589,7 +39589,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="6">
         <v>316</v>
       </c>
@@ -39666,7 +39666,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="6">
         <v>317</v>
       </c>
@@ -39743,7 +39743,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="6">
         <v>318</v>
       </c>
@@ -39820,7 +39820,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="6">
         <v>319</v>
       </c>
@@ -39897,7 +39897,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="6">
         <v>320</v>
       </c>
@@ -39974,7 +39974,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="6">
         <v>321</v>
       </c>
@@ -40051,7 +40051,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="6">
         <v>322</v>
       </c>
@@ -40128,7 +40128,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="6">
         <v>323</v>
       </c>
@@ -40205,7 +40205,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="6">
         <v>324</v>
       </c>
@@ -40282,7 +40282,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="6">
         <v>325</v>
       </c>
@@ -40359,7 +40359,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="6">
         <v>326</v>
       </c>
@@ -40436,7 +40436,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="6">
         <v>327</v>
       </c>
@@ -40513,7 +40513,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="6">
         <v>328</v>
       </c>
@@ -40590,7 +40590,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="6">
         <v>329</v>
       </c>
@@ -40667,7 +40667,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="6">
         <v>330</v>
       </c>
@@ -40744,7 +40744,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="6">
         <v>331</v>
       </c>
@@ -40821,7 +40821,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="6">
         <v>332</v>
       </c>
@@ -40898,7 +40898,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="6">
         <v>333</v>
       </c>
@@ -40975,7 +40975,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="6">
         <v>334</v>
       </c>
@@ -41052,7 +41052,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="6">
         <v>335</v>
       </c>
@@ -41129,7 +41129,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="6">
         <v>336</v>
       </c>
@@ -41206,7 +41206,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="6">
         <v>337</v>
       </c>
@@ -41283,7 +41283,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="6">
         <v>338</v>
       </c>
@@ -41360,7 +41360,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="6">
         <v>339</v>
       </c>
@@ -41437,7 +41437,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="6">
         <v>340</v>
       </c>
@@ -41514,7 +41514,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="6">
         <v>341</v>
       </c>
@@ -41591,7 +41591,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="6">
         <v>342</v>
       </c>
@@ -41668,7 +41668,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="6">
         <v>343</v>
       </c>
@@ -41745,7 +41745,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="6">
         <v>344</v>
       </c>
@@ -41822,7 +41822,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="6">
         <v>345</v>
       </c>
@@ -41899,7 +41899,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="6">
         <v>346</v>
       </c>
@@ -41976,7 +41976,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="6">
         <v>347</v>
       </c>
@@ -42053,7 +42053,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="6">
         <v>348</v>
       </c>
@@ -42130,7 +42130,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="6">
         <v>349</v>
       </c>
@@ -42207,7 +42207,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="6">
         <v>350</v>
       </c>
@@ -42284,7 +42284,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="6">
         <v>351</v>
       </c>
@@ -42361,7 +42361,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="6">
         <v>352</v>
       </c>
@@ -42438,7 +42438,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="6">
         <v>353</v>
       </c>
@@ -42515,7 +42515,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="6">
         <v>354</v>
       </c>
@@ -42592,7 +42592,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="6">
         <v>355</v>
       </c>
@@ -42669,7 +42669,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="6">
         <v>356</v>
       </c>
@@ -42746,7 +42746,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="6">
         <v>357</v>
       </c>
@@ -42823,7 +42823,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="6">
         <v>358</v>
       </c>
@@ -42900,7 +42900,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="6">
         <v>359</v>
       </c>
@@ -42977,7 +42977,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="6">
         <v>360</v>
       </c>
@@ -43054,7 +43054,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="6">
         <v>361</v>
       </c>
@@ -43131,7 +43131,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="6">
         <v>362</v>
       </c>
@@ -43208,7 +43208,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="6">
         <v>363</v>
       </c>
@@ -43285,7 +43285,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="6">
         <v>364</v>
       </c>
@@ -43362,7 +43362,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="6">
         <v>365</v>
       </c>
@@ -43439,7 +43439,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="6">
         <v>366</v>
       </c>
@@ -43516,7 +43516,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="6">
         <v>367</v>
       </c>
@@ -43593,7 +43593,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="6">
         <v>368</v>
       </c>
@@ -43670,7 +43670,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="6">
         <v>369</v>
       </c>
@@ -43747,7 +43747,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="6">
         <v>370</v>
       </c>
@@ -43824,7 +43824,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="6">
         <v>371</v>
       </c>
@@ -43901,7 +43901,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="6">
         <v>372</v>
       </c>
@@ -43978,7 +43978,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="6">
         <v>373</v>
       </c>
@@ -44055,7 +44055,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="6">
         <v>374</v>
       </c>
@@ -44132,7 +44132,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="375" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="6">
         <v>375</v>
       </c>
@@ -44209,7 +44209,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="376" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="6">
         <v>376</v>
       </c>
@@ -44286,7 +44286,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="377" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="6">
         <v>377</v>
       </c>
@@ -44363,7 +44363,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="378" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="6">
         <v>378</v>
       </c>
@@ -44440,7 +44440,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="379" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="6">
         <v>379</v>
       </c>
@@ -44517,7 +44517,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="380" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="6">
         <v>380</v>
       </c>
@@ -44594,7 +44594,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="381" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="6">
         <v>381</v>
       </c>
@@ -44671,7 +44671,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="382" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="6">
         <v>382</v>
       </c>
@@ -44748,7 +44748,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="383" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="6">
         <v>383</v>
       </c>
@@ -44825,7 +44825,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="384" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="6">
         <v>384</v>
       </c>
@@ -44902,7 +44902,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="385" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="6">
         <v>385</v>
       </c>
@@ -44979,7 +44979,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="386" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="6">
         <v>386</v>
       </c>
@@ -45056,7 +45056,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="387" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="6">
         <v>387</v>
       </c>
@@ -45133,7 +45133,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="388" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="6">
         <v>388</v>
       </c>
@@ -45210,7 +45210,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="389" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="6">
         <v>389</v>
       </c>
@@ -45287,7 +45287,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="390" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="6">
         <v>390</v>
       </c>
@@ -45364,7 +45364,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="391" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="6">
         <v>391</v>
       </c>
@@ -45441,7 +45441,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="392" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="6">
         <v>392</v>
       </c>
@@ -45518,7 +45518,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="393" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="6">
         <v>393</v>
       </c>
@@ -45595,7 +45595,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="394" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="6">
         <v>394</v>
       </c>
@@ -45672,7 +45672,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="395" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="6">
         <v>395</v>
       </c>
@@ -45749,7 +45749,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="396" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="6">
         <v>396</v>
       </c>
@@ -45826,7 +45826,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="397" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="6">
         <v>397</v>
       </c>
@@ -45903,7 +45903,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="398" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="6">
         <v>398</v>
       </c>
@@ -45980,7 +45980,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="399" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="6">
         <v>399</v>
       </c>
@@ -46057,7 +46057,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="400" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="6">
         <v>400</v>
       </c>
@@ -46134,7 +46134,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="401" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="6">
         <v>401</v>
       </c>
@@ -46211,7 +46211,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="402" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="6">
         <v>402</v>
       </c>
@@ -46288,7 +46288,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="403" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="6">
         <v>403</v>
       </c>
@@ -46365,7 +46365,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="404" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="6">
         <v>404</v>
       </c>
@@ -46442,7 +46442,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="405" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="6">
         <v>405</v>
       </c>
@@ -46519,7 +46519,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="406" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="6">
         <v>406</v>
       </c>
@@ -46596,7 +46596,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="407" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="6">
         <v>407</v>
       </c>
@@ -46673,7 +46673,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="408" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="6">
         <v>408</v>
       </c>
@@ -46750,7 +46750,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="409" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="6">
         <v>409</v>
       </c>
@@ -46827,7 +46827,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="410" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="6">
         <v>410</v>
       </c>
@@ -46904,7 +46904,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="411" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="6">
         <v>411</v>
       </c>
@@ -46981,7 +46981,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="412" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="6">
         <v>412</v>
       </c>
@@ -47058,7 +47058,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="413" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="6">
         <v>413</v>
       </c>
@@ -47135,7 +47135,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="414" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="6">
         <v>414</v>
       </c>
@@ -47212,7 +47212,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="415" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="6">
         <v>415</v>
       </c>
@@ -47289,7 +47289,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="416" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="6">
         <v>416</v>
       </c>
@@ -47366,7 +47366,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="417" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="6">
         <v>417</v>
       </c>
@@ -47443,7 +47443,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="418" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="6">
         <v>418</v>
       </c>
@@ -47520,7 +47520,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="419" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="6">
         <v>419</v>
       </c>
@@ -47597,7 +47597,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="420" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="6">
         <v>420</v>
       </c>
@@ -47674,7 +47674,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="421" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="6">
         <v>421</v>
       </c>
@@ -47751,7 +47751,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="422" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="6">
         <v>422</v>
       </c>
@@ -47828,7 +47828,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="423" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="6">
         <v>423</v>
       </c>
@@ -47905,7 +47905,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="424" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="6">
         <v>424</v>
       </c>
@@ -47982,7 +47982,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="425" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="6">
         <v>425</v>
       </c>
@@ -48059,7 +48059,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="426" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="6">
         <v>426</v>
       </c>
@@ -48136,7 +48136,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="427" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="6">
         <v>427</v>
       </c>
@@ -48213,7 +48213,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="428" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="6">
         <v>428</v>
       </c>
@@ -48290,7 +48290,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="429" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="6">
         <v>429</v>
       </c>
@@ -48367,7 +48367,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="430" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="6">
         <v>430</v>
       </c>
@@ -48444,7 +48444,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="431" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="6">
         <v>431</v>
       </c>
@@ -48521,7 +48521,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="432" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="6">
         <v>432</v>
       </c>
@@ -48598,7 +48598,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="433" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="6">
         <v>433</v>
       </c>
@@ -48675,7 +48675,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="434" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="6">
         <v>434</v>
       </c>
@@ -48752,7 +48752,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="435" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="6">
         <v>435</v>
       </c>
@@ -48829,7 +48829,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="436" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="6">
         <v>436</v>
       </c>
@@ -48906,7 +48906,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="437" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="6">
         <v>437</v>
       </c>
@@ -48983,7 +48983,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="438" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="6">
         <v>438</v>
       </c>
@@ -49060,7 +49060,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="439" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="6">
         <v>439</v>
       </c>
@@ -49137,7 +49137,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="440" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="6">
         <v>440</v>
       </c>
@@ -49214,7 +49214,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="441" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="6">
         <v>441</v>
       </c>
@@ -49291,7 +49291,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="442" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="6">
         <v>442</v>
       </c>
@@ -49368,7 +49368,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="443" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="6">
         <v>443</v>
       </c>
@@ -49445,7 +49445,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="444" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="6">
         <v>444</v>
       </c>
@@ -49522,7 +49522,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="445" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="6">
         <v>445</v>
       </c>
@@ -49599,7 +49599,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="446" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="6">
         <v>446</v>
       </c>
@@ -49676,7 +49676,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="447" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="6">
         <v>447</v>
       </c>
@@ -49753,7 +49753,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="448" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="6">
         <v>448</v>
       </c>
@@ -49830,7 +49830,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="449" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="6">
         <v>449</v>
       </c>
@@ -49907,7 +49907,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="450" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="6">
         <v>450</v>
       </c>
@@ -49984,7 +49984,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="451" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="6">
         <v>451</v>
       </c>
@@ -50061,7 +50061,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="452" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="6">
         <v>452</v>
       </c>
@@ -50138,7 +50138,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="453" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="6">
         <v>453</v>
       </c>
@@ -50215,7 +50215,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="454" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="6">
         <v>454</v>
       </c>
@@ -50292,7 +50292,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="455" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="6">
         <v>455</v>
       </c>
@@ -50369,7 +50369,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="456" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="6">
         <v>456</v>
       </c>
@@ -50446,7 +50446,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="457" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="6">
         <v>457</v>
       </c>
@@ -50523,7 +50523,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="458" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="6">
         <v>458</v>
       </c>
@@ -50600,7 +50600,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="459" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="6">
         <v>459</v>
       </c>
@@ -50677,7 +50677,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="460" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="6">
         <v>460</v>
       </c>
@@ -50754,7 +50754,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="461" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="6">
         <v>461</v>
       </c>
@@ -50831,7 +50831,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="462" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="6">
         <v>462</v>
       </c>
@@ -50908,7 +50908,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="463" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="6">
         <v>463</v>
       </c>
@@ -50985,7 +50985,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="464" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="6">
         <v>464</v>
       </c>
@@ -51062,7 +51062,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="465" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="6">
         <v>465</v>
       </c>
@@ -51139,7 +51139,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="466" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="6">
         <v>466</v>
       </c>
@@ -51216,7 +51216,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="467" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="6">
         <v>467</v>
       </c>
@@ -51293,7 +51293,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="468" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="6">
         <v>468</v>
       </c>
@@ -51370,7 +51370,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="469" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="6">
         <v>469</v>
       </c>
@@ -51447,7 +51447,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="470" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="6">
         <v>470</v>
       </c>
@@ -51524,7 +51524,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="471" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="6">
         <v>471</v>
       </c>
@@ -51601,7 +51601,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="472" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="6">
         <v>472</v>
       </c>
@@ -51678,7 +51678,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="473" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="6">
         <v>473</v>
       </c>
@@ -51755,7 +51755,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="474" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="6">
         <v>474</v>
       </c>
@@ -51832,7 +51832,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="475" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="6">
         <v>475</v>
       </c>
@@ -51909,7 +51909,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="476" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="6">
         <v>476</v>
       </c>
@@ -51986,7 +51986,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="477" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="6">
         <v>477</v>
       </c>
@@ -52063,7 +52063,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="478" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="6">
         <v>478</v>
       </c>
@@ -52140,7 +52140,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="479" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="6">
         <v>479</v>
       </c>
@@ -52217,7 +52217,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="480" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="6">
         <v>480</v>
       </c>
@@ -52294,7 +52294,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="481" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="6">
         <v>481</v>
       </c>
@@ -52371,7 +52371,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="482" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="6">
         <v>482</v>
       </c>
@@ -52448,7 +52448,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="483" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="6">
         <v>483</v>
       </c>
@@ -52525,7 +52525,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="484" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="6">
         <v>484</v>
       </c>
@@ -52602,7 +52602,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="485" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="6">
         <v>485</v>
       </c>
@@ -52679,7 +52679,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="486" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="6">
         <v>486</v>
       </c>
@@ -52756,7 +52756,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="487" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="6">
         <v>487</v>
       </c>
@@ -52833,7 +52833,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="488" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="6">
         <v>488</v>
       </c>
@@ -52910,7 +52910,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="489" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="6">
         <v>489</v>
       </c>
@@ -52987,7 +52987,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="490" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="6">
         <v>490</v>
       </c>
@@ -53064,7 +53064,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="491" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="6">
         <v>491</v>
       </c>
@@ -53141,7 +53141,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="492" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="6">
         <v>492</v>
       </c>
@@ -53218,7 +53218,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="493" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="6">
         <v>493</v>
       </c>
@@ -53295,7 +53295,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="494" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="6">
         <v>494</v>
       </c>
@@ -53372,7 +53372,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="495" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="6">
         <v>495</v>
       </c>
@@ -53449,7 +53449,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="496" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="6">
         <v>496</v>
       </c>
@@ -53526,7 +53526,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="497" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="6">
         <v>497</v>
       </c>
@@ -53603,7 +53603,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="498" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="6">
         <v>498</v>
       </c>
@@ -53680,7 +53680,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="499" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="6">
         <v>499</v>
       </c>
@@ -53757,7 +53757,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="6">
         <v>500</v>
       </c>
@@ -53834,7 +53834,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="501" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="6">
         <v>501</v>
       </c>
@@ -53911,7 +53911,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="502" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="6">
         <v>502</v>
       </c>
@@ -53988,7 +53988,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="503" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="6">
         <v>503</v>
       </c>
@@ -54065,7 +54065,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="504" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="6">
         <v>504</v>
       </c>
@@ -54142,7 +54142,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="505" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="6">
         <v>505</v>
       </c>
@@ -54219,7 +54219,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="506" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="6">
         <v>506</v>
       </c>
@@ -54296,7 +54296,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="507" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="6">
         <v>507</v>
       </c>
@@ -54373,7 +54373,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="508" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="6">
         <v>508</v>
       </c>
@@ -54450,7 +54450,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="509" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="6">
         <v>509</v>
       </c>
@@ -54527,7 +54527,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="510" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="6">
         <v>510</v>
       </c>
@@ -54604,7 +54604,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="511" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="6">
         <v>511</v>
       </c>
@@ -54681,7 +54681,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="512" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="6">
         <v>512</v>
       </c>
@@ -54758,7 +54758,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="513" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="6">
         <v>513</v>
       </c>
@@ -54835,7 +54835,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="514" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="6">
         <v>514</v>
       </c>
@@ -54912,7 +54912,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="515" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="6">
         <v>515</v>
       </c>
@@ -54989,7 +54989,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="516" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="6">
         <v>516</v>
       </c>
@@ -55066,7 +55066,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="517" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="6">
         <v>517</v>
       </c>
@@ -55143,7 +55143,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="518" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="6">
         <v>518</v>
       </c>
@@ -55220,7 +55220,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="519" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="6">
         <v>519</v>
       </c>
@@ -55297,7 +55297,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="520" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="6">
         <v>520</v>
       </c>
@@ -55374,7 +55374,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="521" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="6">
         <v>521</v>
       </c>
@@ -55451,7 +55451,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="522" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="6">
         <v>522</v>
       </c>
@@ -55528,7 +55528,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="523" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="6">
         <v>523</v>
       </c>
@@ -55605,7 +55605,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="524" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="6">
         <v>524</v>
       </c>
@@ -55682,7 +55682,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="525" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="6">
         <v>525</v>
       </c>
@@ -55759,7 +55759,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="526" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="6">
         <v>526</v>
       </c>
@@ -55836,7 +55836,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="527" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="6">
         <v>527</v>
       </c>
@@ -55913,7 +55913,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="528" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="6">
         <v>528</v>
       </c>
@@ -55990,7 +55990,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="529" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="6">
         <v>529</v>
       </c>
@@ -56067,7 +56067,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="530" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="6">
         <v>530</v>
       </c>
@@ -56144,7 +56144,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="531" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="6">
         <v>531</v>
       </c>
@@ -56221,7 +56221,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="532" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="6">
         <v>532</v>
       </c>
@@ -56298,7 +56298,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="533" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="6">
         <v>533</v>
       </c>
@@ -56375,7 +56375,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="534" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="6">
         <v>534</v>
       </c>
@@ -56452,7 +56452,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="535" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="6">
         <v>535</v>
       </c>
@@ -56529,7 +56529,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="536" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="6">
         <v>536</v>
       </c>
@@ -56606,7 +56606,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="537" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="6">
         <v>537</v>
       </c>
@@ -56683,7 +56683,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="538" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="6">
         <v>538</v>
       </c>
@@ -56760,7 +56760,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="539" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="6">
         <v>539</v>
       </c>
@@ -56837,7 +56837,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="540" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="6">
         <v>540</v>
       </c>
@@ -56914,7 +56914,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="541" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="6">
         <v>541</v>
       </c>
@@ -56991,7 +56991,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="542" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="6">
         <v>542</v>
       </c>
@@ -57068,7 +57068,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="543" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="6">
         <v>543</v>
       </c>
@@ -57145,7 +57145,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="544" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="6">
         <v>544</v>
       </c>
@@ -57222,7 +57222,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="545" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="6">
         <v>545</v>
       </c>
@@ -57299,7 +57299,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="546" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="6">
         <v>546</v>
       </c>
@@ -57376,7 +57376,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="547" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="6">
         <v>547</v>
       </c>
@@ -57453,7 +57453,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="548" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="6">
         <v>548</v>
       </c>
@@ -57530,7 +57530,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="549" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="6">
         <v>549</v>
       </c>
@@ -57607,7 +57607,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="550" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="6">
         <v>550</v>
       </c>
@@ -57684,7 +57684,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="551" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="6">
         <v>551</v>
       </c>
@@ -57761,7 +57761,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="552" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="6">
         <v>552</v>
       </c>
@@ -57838,7 +57838,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="553" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="6">
         <v>553</v>
       </c>
@@ -57915,7 +57915,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="554" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="6">
         <v>554</v>
       </c>
@@ -57992,7 +57992,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="555" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="6">
         <v>555</v>
       </c>
@@ -58069,7 +58069,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="556" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="6">
         <v>556</v>
       </c>
@@ -58146,7 +58146,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="557" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="6">
         <v>557</v>
       </c>
@@ -58223,7 +58223,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="558" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="6">
         <v>558</v>
       </c>
@@ -58300,7 +58300,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="559" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="6">
         <v>559</v>
       </c>
@@ -58377,7 +58377,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="560" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="6">
         <v>560</v>
       </c>
@@ -58454,7 +58454,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="561" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="6">
         <v>561</v>
       </c>
@@ -58531,7 +58531,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="562" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="6">
         <v>562</v>
       </c>
@@ -58608,7 +58608,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="563" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="6">
         <v>563</v>
       </c>
@@ -58685,7 +58685,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="564" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="6">
         <v>564</v>
       </c>
@@ -58762,7 +58762,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="565" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="6">
         <v>565</v>
       </c>
@@ -58839,7 +58839,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="566" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="6">
         <v>566</v>
       </c>
@@ -58916,7 +58916,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="567" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="6">
         <v>567</v>
       </c>
@@ -58993,7 +58993,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="568" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="6">
         <v>568</v>
       </c>
@@ -59070,7 +59070,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="569" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="6">
         <v>569</v>
       </c>
@@ -59147,7 +59147,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="570" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="6">
         <v>570</v>
       </c>
@@ -59224,7 +59224,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="571" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="6">
         <v>571</v>
       </c>
@@ -59301,7 +59301,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="572" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="6">
         <v>572</v>
       </c>
@@ -59378,7 +59378,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="573" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="6">
         <v>573</v>
       </c>
@@ -59455,7 +59455,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="574" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="6">
         <v>574</v>
       </c>
@@ -59532,7 +59532,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="575" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="6">
         <v>575</v>
       </c>
@@ -59609,7 +59609,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="576" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="6">
         <v>576</v>
       </c>
@@ -59686,7 +59686,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="577" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="6">
         <v>577</v>
       </c>
@@ -59763,7 +59763,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="578" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="6">
         <v>578</v>
       </c>
@@ -59840,7 +59840,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="579" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="6">
         <v>579</v>
       </c>
@@ -59917,7 +59917,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="580" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="6">
         <v>580</v>
       </c>
@@ -59994,7 +59994,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="581" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="6">
         <v>581</v>
       </c>
@@ -60071,7 +60071,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="582" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="6">
         <v>582</v>
       </c>
@@ -60148,7 +60148,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="583" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="6">
         <v>583</v>
       </c>
@@ -60225,7 +60225,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="584" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="6">
         <v>584</v>
       </c>
@@ -60302,7 +60302,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="585" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="6">
         <v>585</v>
       </c>
@@ -60379,7 +60379,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="586" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="6">
         <v>586</v>
       </c>
@@ -60456,7 +60456,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="587" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="6">
         <v>587</v>
       </c>
@@ -60533,7 +60533,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="588" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="6">
         <v>588</v>
       </c>
@@ -60610,7 +60610,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="589" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="6">
         <v>589</v>
       </c>
@@ -60687,7 +60687,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="590" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="6">
         <v>590</v>
       </c>
@@ -60764,7 +60764,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="591" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="6">
         <v>591</v>
       </c>
@@ -60841,7 +60841,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="592" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="6">
         <v>592</v>
       </c>
@@ -60918,7 +60918,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="593" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="6">
         <v>593</v>
       </c>
@@ -60995,7 +60995,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="594" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="6">
         <v>594</v>
       </c>
@@ -61072,7 +61072,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="595" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="6">
         <v>595</v>
       </c>
@@ -61149,7 +61149,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="596" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="6">
         <v>596</v>
       </c>
@@ -61226,7 +61226,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="597" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="6">
         <v>597</v>
       </c>
@@ -61303,7 +61303,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="598" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="6">
         <v>598</v>
       </c>
@@ -61380,7 +61380,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="599" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="6">
         <v>599</v>
       </c>
@@ -61457,7 +61457,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="600" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="6">
         <v>600</v>
       </c>
@@ -61534,7 +61534,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="601" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="6">
         <v>601</v>
       </c>
@@ -61611,7 +61611,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="602" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="6">
         <v>602</v>
       </c>
@@ -61688,7 +61688,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="603" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="6">
         <v>603</v>
       </c>
@@ -61765,7 +61765,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="604" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="6">
         <v>604</v>
       </c>
@@ -61842,7 +61842,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="605" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="6">
         <v>605</v>
       </c>
@@ -61919,7 +61919,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="606" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="6">
         <v>606</v>
       </c>
@@ -61996,7 +61996,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="607" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="6">
         <v>607</v>
       </c>
@@ -62073,7 +62073,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="608" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="6">
         <v>608</v>
       </c>
@@ -62150,7 +62150,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="609" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="6">
         <v>609</v>
       </c>
@@ -62227,7 +62227,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="610" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="6">
         <v>610</v>
       </c>
@@ -62304,7 +62304,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="611" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="6">
         <v>611</v>
       </c>
@@ -62381,7 +62381,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="612" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="6">
         <v>612</v>
       </c>
@@ -62458,7 +62458,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="613" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="6">
         <v>613</v>
       </c>
@@ -62535,7 +62535,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="614" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="6">
         <v>614</v>
       </c>
@@ -62612,7 +62612,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="615" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="6">
         <v>615</v>
       </c>
@@ -62689,7 +62689,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="616" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="6">
         <v>616</v>
       </c>
@@ -62766,7 +62766,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="617" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="6">
         <v>617</v>
       </c>
@@ -62843,7 +62843,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="618" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="6">
         <v>618</v>
       </c>
@@ -62920,7 +62920,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="619" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="6">
         <v>619</v>
       </c>
@@ -62997,7 +62997,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="620" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="6">
         <v>620</v>
       </c>
@@ -63074,7 +63074,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="621" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="6">
         <v>621</v>
       </c>
@@ -63151,7 +63151,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="622" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="6">
         <v>622</v>
       </c>
@@ -63228,7 +63228,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="623" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="6">
         <v>623</v>
       </c>
@@ -63305,7 +63305,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="624" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="6">
         <v>624</v>
       </c>
@@ -63382,7 +63382,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="625" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="6">
         <v>625</v>
       </c>
@@ -63459,7 +63459,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="626" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="6">
         <v>626</v>
       </c>
@@ -63536,7 +63536,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="627" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="6">
         <v>627</v>
       </c>
@@ -63613,7 +63613,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="628" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="6">
         <v>628</v>
       </c>
@@ -63690,7 +63690,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="629" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="6">
         <v>629</v>
       </c>
@@ -63767,7 +63767,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="630" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="6">
         <v>630</v>
       </c>
@@ -63844,7 +63844,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="631" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="6">
         <v>631</v>
       </c>
@@ -63921,7 +63921,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="632" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="6">
         <v>632</v>
       </c>
@@ -63998,7 +63998,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="633" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="6">
         <v>633</v>
       </c>
@@ -64075,7 +64075,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="634" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="6">
         <v>634</v>
       </c>
@@ -64152,7 +64152,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="635" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="6">
         <v>635</v>
       </c>
@@ -64229,7 +64229,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="636" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="6">
         <v>636</v>
       </c>
@@ -64306,7 +64306,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="637" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="6">
         <v>637</v>
       </c>
@@ -64383,7 +64383,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="638" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="6">
         <v>638</v>
       </c>
@@ -64460,7 +64460,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="639" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="6">
         <v>639</v>
       </c>
@@ -64537,7 +64537,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="640" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="6">
         <v>640</v>
       </c>
@@ -64614,7 +64614,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="641" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="6">
         <v>641</v>
       </c>
@@ -64691,7 +64691,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="642" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="6">
         <v>642</v>
       </c>
@@ -64768,7 +64768,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="643" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="6">
         <v>643</v>
       </c>
@@ -64845,7 +64845,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="644" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="6">
         <v>644</v>
       </c>
@@ -64922,7 +64922,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="645" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="6">
         <v>645</v>
       </c>
@@ -64999,7 +64999,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="646" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="6">
         <v>646</v>
       </c>
@@ -65076,7 +65076,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="647" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="6">
         <v>647</v>
       </c>
@@ -65153,7 +65153,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="648" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="6">
         <v>648</v>
       </c>
@@ -65230,7 +65230,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="649" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="6">
         <v>649</v>
       </c>
@@ -65307,7 +65307,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="650" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="6">
         <v>650</v>
       </c>
@@ -65384,7 +65384,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="651" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="6">
         <v>651</v>
       </c>
@@ -65461,7 +65461,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="652" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="6">
         <v>652</v>
       </c>
@@ -65538,7 +65538,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="653" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="6">
         <v>653</v>
       </c>
@@ -65615,7 +65615,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="654" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="6">
         <v>654</v>
       </c>
@@ -65692,7 +65692,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="655" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="6">
         <v>655</v>
       </c>
@@ -65769,7 +65769,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="656" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="6">
         <v>656</v>
       </c>
@@ -65846,7 +65846,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="657" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="6">
         <v>657</v>
       </c>
@@ -65923,7 +65923,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="658" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="6">
         <v>658</v>
       </c>
@@ -66000,7 +66000,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="659" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="6">
         <v>659</v>
       </c>
@@ -66077,7 +66077,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="660" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="6">
         <v>660</v>
       </c>
@@ -66154,7 +66154,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="661" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="6">
         <v>661</v>
       </c>
@@ -66231,7 +66231,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="662" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="6">
         <v>662</v>
       </c>
@@ -66308,7 +66308,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="663" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="6">
         <v>663</v>
       </c>
@@ -66385,7 +66385,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="664" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="6">
         <v>664</v>
       </c>
@@ -66462,7 +66462,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="665" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="6">
         <v>665</v>
       </c>
@@ -66539,7 +66539,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="666" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="6">
         <v>666</v>
       </c>
@@ -66616,7 +66616,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="667" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="6">
         <v>667</v>
       </c>
@@ -66693,7 +66693,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="668" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="6">
         <v>668</v>
       </c>
@@ -66770,7 +66770,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="669" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="6">
         <v>669</v>
       </c>
@@ -66847,7 +66847,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="670" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="6">
         <v>670</v>
       </c>
@@ -66924,7 +66924,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="671" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="6">
         <v>671</v>
       </c>
@@ -67001,7 +67001,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="672" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="6">
         <v>672</v>
       </c>
@@ -67078,7 +67078,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="673" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="6">
         <v>673</v>
       </c>
@@ -67155,7 +67155,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="674" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="6">
         <v>674</v>
       </c>
@@ -67232,7 +67232,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="675" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="6">
         <v>675</v>
       </c>
@@ -67309,7 +67309,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="676" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="6">
         <v>676</v>
       </c>
@@ -67386,7 +67386,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="677" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="6">
         <v>677</v>
       </c>
@@ -67463,7 +67463,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="678" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="6">
         <v>678</v>
       </c>
@@ -67540,7 +67540,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="679" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="6">
         <v>679</v>
       </c>
@@ -67617,7 +67617,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="680" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="6">
         <v>680</v>
       </c>
@@ -67694,7 +67694,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="681" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="6">
         <v>681</v>
       </c>
@@ -67771,7 +67771,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="682" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="6">
         <v>682</v>
       </c>
@@ -67848,7 +67848,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="683" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="6">
         <v>683</v>
       </c>
@@ -67925,7 +67925,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="684" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="6">
         <v>684</v>
       </c>
@@ -68002,7 +68002,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="685" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="6">
         <v>685</v>
       </c>
@@ -68079,7 +68079,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="686" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="6">
         <v>686</v>
       </c>
@@ -68156,7 +68156,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="687" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="6">
         <v>687</v>
       </c>
@@ -68233,7 +68233,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="688" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="6">
         <v>688</v>
       </c>
@@ -68310,7 +68310,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="689" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="6">
         <v>689</v>
       </c>
@@ -68387,7 +68387,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="690" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="6">
         <v>690</v>
       </c>
@@ -68464,7 +68464,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="691" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="6">
         <v>691</v>
       </c>
@@ -68541,7 +68541,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="692" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="6">
         <v>692</v>
       </c>
@@ -68618,7 +68618,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="693" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="6">
         <v>693</v>
       </c>
@@ -68695,7 +68695,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="694" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="6">
         <v>694</v>
       </c>
@@ -68772,7 +68772,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="695" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="6">
         <v>695</v>
       </c>
@@ -68849,7 +68849,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="696" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="6">
         <v>696</v>
       </c>
@@ -68926,7 +68926,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="697" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="6">
         <v>697</v>
       </c>
@@ -69003,7 +69003,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="698" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="6">
         <v>698</v>
       </c>
@@ -69080,7 +69080,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="699" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="6">
         <v>699</v>
       </c>
@@ -69157,7 +69157,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="700" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="6">
         <v>700</v>
       </c>
@@ -69234,7 +69234,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="701" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="6">
         <v>701</v>
       </c>
@@ -69311,7 +69311,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="702" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="6">
         <v>702</v>
       </c>
@@ -69388,7 +69388,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="703" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="6">
         <v>703</v>
       </c>
@@ -69465,7 +69465,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="704" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="6">
         <v>704</v>
       </c>
@@ -69542,7 +69542,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="705" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="6">
         <v>705</v>
       </c>
@@ -69619,7 +69619,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="706" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="6">
         <v>706</v>
       </c>
@@ -69696,7 +69696,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="707" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="6">
         <v>707</v>
       </c>
@@ -69773,7 +69773,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="708" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="6">
         <v>708</v>
       </c>
@@ -69850,7 +69850,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="709" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="6">
         <v>709</v>
       </c>
@@ -69927,7 +69927,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="710" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="6">
         <v>710</v>
       </c>
@@ -70004,7 +70004,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="711" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="6">
         <v>711</v>
       </c>
@@ -70081,7 +70081,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="712" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="6">
         <v>712</v>
       </c>
@@ -70158,7 +70158,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="713" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="6">
         <v>713</v>
       </c>
@@ -70235,7 +70235,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="714" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="6">
         <v>714</v>
       </c>
@@ -70312,7 +70312,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="715" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="6">
         <v>715</v>
       </c>
@@ -70389,7 +70389,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="716" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="6">
         <v>716</v>
       </c>
@@ -70466,7 +70466,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="717" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="6">
         <v>717</v>
       </c>
@@ -70543,7 +70543,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="718" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="6">
         <v>718</v>
       </c>
@@ -70620,7 +70620,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="719" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="6">
         <v>719</v>
       </c>
@@ -70697,7 +70697,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="720" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="6">
         <v>720</v>
       </c>
@@ -70774,7 +70774,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="721" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="6">
         <v>721</v>
       </c>
@@ -70851,7 +70851,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="722" spans="1:25" ht="6.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:25" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="6">
         <v>722</v>
       </c>
